--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Reb0c41b0e535425e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R24ef06a1a8a8465e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R5ca34f4559584f79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R44cc960f30e444db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R7c673aebe65d4fef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R5128b519b4164f6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rc046f837cd0c43a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R16f1c3fcb54b4f9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R39c7ac30dd4f4626"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Raa02d98ccba84d04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rb49767a7b0094bea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R77d85c6c0d4c43ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R035f15c4f4544a28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rc979030c4c5e40bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Ra24d36874cbd4a3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R9131dd8c6ca9413d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Ra7742a5233b34b30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R68b6253122b24608"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rb2eef1e1397f48ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rce3c64ae7c2f46d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R51c3ffb6f2e14070"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Ra8ef8564b9444f1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rb2068dd5bb2146d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R0c2e91afa1dc4a1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Radf029c55689415d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Rc91ff6af251846cf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5000,10 +5000,8 @@
           <x:t xml:space="preserve">Nature Strikes Back</x:t>
         </x:is>
       </x:c>
-      <x:c r="E9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Placeholder shell — full design/coding required</x:t>
-        </x:is>
+      <x:c r="E9" s="31" t="str">
+        <x:v>Implemented — needs machine playtest/polish</x:v>
       </x:c>
       <x:c r="F9" s="85" t="n"/>
       <x:c r="G9" s="85" t="n"/>
@@ -5044,10 +5042,8 @@
           <x:t xml:space="preserve">Invasion from Everywhere</x:t>
         </x:is>
       </x:c>
-      <x:c r="E10" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Placeholder shell — full design/coding required</x:t>
-        </x:is>
+      <x:c r="E10" s="31" t="str">
+        <x:v>Implemented — needs machine playtest/polish</x:v>
       </x:c>
       <x:c r="F10" s="85" t="n"/>
       <x:c r="G10" s="85" t="n"/>
@@ -10330,10 +10326,8 @@
           <x:t xml:space="preserve">No individual Case File powers. Each Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files; 0–500K). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:t>
         </x:is>
       </x:c>
-      <x:c r="G9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Explicit placeholder shell; full design and coding required.</x:t>
-        </x:is>
+      <x:c r="G9" s="31" t="str">
+        <x:v>Implemented repeating elemental-chain multiball; Blotto attack now accumulates up to three simultaneous solid-purple blocked zones during the thaw stage, with attack cadence 8s / 7s / 6s by cycle. Star clears all blocked zones and resets the timer. Needs machine playtest/polish.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -10365,10 +10359,8 @@
           <x:t xml:space="preserve">No individual Case File powers. Each Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files; 0–500K). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:t>
         </x:is>
       </x:c>
-      <x:c r="G10" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Explicit placeholder shell; full design and coding required.</x:t>
-        </x:is>
+      <x:c r="G10" s="31" t="str">
+        <x:v>Implemented 3-ball VUK/saucer relay wizard cycling Igor, Molemen, and DeVargas lower phases into escalating Doctor Atlantean rooftop jackpots; needs machine playtest/polish.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
